--- a/BaseTraining/unit5_buildImage/unit5_buildimage.xlsx
+++ b/BaseTraining/unit5_buildImage/unit5_buildimage.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1742C51F-647B-41F4-AECA-16B3D1D94FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="MucLuc" sheetId="11" r:id="rId1"/>
@@ -30,47 +29,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="591">
   <si>
     <t>📦 Toolchain để build image là gì?</t>
   </si>
   <si>
-    <r>
-      <t>Toolchain</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> là </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bộ công cụ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (tool + chain = chuỗi công cụ) được dùng để:</t>
-    </r>
-  </si>
-  <si>
     <t>Biên dịch (compile),</t>
   </si>
   <si>
@@ -80,82 +43,9 @@
     <t>Tạo binary (file thực thi),</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Và đóng gói thành </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>firmware image</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hoặc </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Linux image</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>Đặc biệt:</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Trong Embedded Linux (và nhiều hệ thống nhúng khác), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>toolchain thường phải cross-compile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> — tức là build cho một kiến trúc khác (ví dụ: build trên PC x86_64 → chạy trên ARM, MIPS, RISC-V...).</t>
-    </r>
-  </si>
-  <si>
     <t>📋 Một bộ Toolchain điển hình gồm các thành phần:</t>
   </si>
   <si>
@@ -201,32 +91,6 @@
     <t>Hỗ trợ debug code (nếu cần)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">➔ Tất cả kết hợp lại thành </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Toolchain</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>📷 Ví dụ thực tế về Toolchain:</t>
   </si>
   <si>
@@ -257,45 +121,7 @@
     <t>x86_64</t>
   </si>
   <si>
-    <r>
-      <t>gcc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (nếu cùng máy)</t>
-    </r>
-  </si>
-  <si>
     <t>🔥 Khi nào cần Toolchain?</t>
-  </si>
-  <si>
-    <r>
-      <t>Khi build kernel (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>make ARCH=arm CROSS_COMPILE=arm-linux-gnueabihf-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <t>Khi build rootfs (Busybox, Buildroot, Yocto...).</t>
@@ -6733,12 +6559,1396 @@
   <si>
     <t>Cross Compiler</t>
   </si>
+  <si>
+    <r>
+      <t>Toolchain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bộ công cụ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tool + chain = chuỗi công cụ) được dùng để:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Và đóng gói thành </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firmware image</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linux image</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong Embedded Linux (và nhiều hệ thống nhúng khác), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toolchain thường phải cross-compile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — tức là build cho một kiến trúc khác (ví dụ: build trên PC x86_64 → chạy trên ARM, MIPS, RISC-V...).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">➔ Tất cả kết hợp lại thành </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Toolchain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>gcc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (nếu cùng máy)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Khi build kernel (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>make ARCH=arm CROSS_COMPILE=arm-linux-gnueabihf-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>file thực thi, thư viện, script, cấu hình</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mà user-space cần để hoạt động.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kernel chỉ biết chạy và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mount</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> root filesystem.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Còn các lệnh như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ls</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bash</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>systemd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>udevd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ifconfig</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ssh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, … đều nằm trong </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rootfs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>🧩 1️⃣ Tổng quan: 4 giai đoạn chính của quá trình boot Linux trên board nhúng</t>
+  </si>
+  <si>
+    <t>┌────────────────────────────┐</t>
+  </si>
+  <si>
+    <t>│ 1. Boot ROM (on-chip)      │  → Nạp bootloader bước 1 (SPL/MLO)</t>
+  </si>
+  <si>
+    <t>│ 2. U-Boot (bootloader)     │  → Nạp kernel + DTB + initramfs</t>
+  </si>
+  <si>
+    <t>│ 3. Kernel (Linux core)     │  → Khởi tạo phần cứng, driver, process 0/1</t>
+  </si>
+  <si>
+    <t>│ 4. RootFS &amp; User space     │  → Mount rootfs, chạy /sbin/init, login shell</t>
+  </si>
+  <si>
+    <t>└────────────────────────────┘</t>
+  </si>
+  <si>
+    <t>⚙️ 2️⃣ Giai đoạn chi tiết</t>
+  </si>
+  <si>
+    <t>🔹 Bước 1 – Boot ROM (tích hợp trong SoC)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi bật nguồn, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Boot ROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (nằm trong chip) là code đầu tiên chạy.</t>
+    </r>
+  </si>
+  <si>
+    <t>Nó dò thiết bị boot (SD, eMMC, SPI, USB, UART…).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nạp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>U-Boot SPL (MLO)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào RAM và nhảy vào đó.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">📍 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Trên BeagleBone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>MLO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nằm trong FAT boot partition.</t>
+    </r>
+  </si>
+  <si>
+    <t>🔹 Bước 2 – U-Boot (Bootloader chính)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SPL khởi tạo RAM → load </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>U-Boot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đầy đủ vào RAM.</t>
+    </r>
+  </si>
+  <si>
+    <t>U-Boot thực hiện:</t>
+  </si>
+  <si>
+    <t>Thiết lập xung nhịp, DDR, clock, UART, v.v.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đọc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kernel image (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>zImage</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>uImage</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Device Tree Blob (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.dtb</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rootfs hoặc initramfs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> từ SD/eMMC/NFS.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Thiết lập tham số boot (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootargs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), ví dụ:</t>
+    </r>
+  </si>
+  <si>
+    <t>console=ttyO0,115200 root=/dev/mmcblk0p2 rw rootwait</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gọi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bootm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chuyển quyền điều khiển cho kernel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>📍 Kết quả: kernel được load vào RAM, sẵn sàng chạy.</t>
+  </si>
+  <si>
+    <t>🔹 Bước 3 – Kernel khởi động (Linux kernel space)</t>
+  </si>
+  <si>
+    <t>Khi kernel chạy, nó làm những việc sau:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Thiết lập bộ nhớ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (page table, MMU).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Khởi tạo driver cơ bản</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (UART, GPIO, I2C, MMC, network, timer…).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Mount rootfs tạm (initramfs/rootfs ramfs)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Tạo process đầu tiên (PID 0)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>swapper / idle task</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Tạo process thứ hai (PID 1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kernel_init</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. kernel_init()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → gọi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>do_execve("/sbin/init")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (từ rootfs thật).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">📍 Nếu kernel không tìm thấy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/sbin/init</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, sẽ báo lỗi:</t>
+    </r>
+  </si>
+  <si>
+    <t>Kernel panic - not syncing: No init found. Try passing init= option to kernel.</t>
+  </si>
+  <si>
+    <t>🔹 Bước 4 – Mount RootFS và khởi động User-Space</t>
+  </si>
+  <si>
+    <t>Khi kernel chuyển sang user-space:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Mount root filesystem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>root=/dev/mmcblk0p2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc NFS, …).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Thực thi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/sbin/init</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (chính là process 1 trong user-space).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. init</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>systemd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>busybox init</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>runit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>…)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chạy script </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/etc/inittab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/etc/systemd/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mount các phân vùng phụ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/proc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/sys</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/dev</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, …)</t>
+    </r>
+  </si>
+  <si>
+    <t>Bật network, SSH, dịch vụ nền</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khởi chạy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>getty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để cung cấp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>login shell</t>
+    </r>
+  </si>
+  <si>
+    <t>📍 Kết quả: bạn thấy prompt:</t>
+  </si>
+  <si>
+    <t>debian@beaglebone:~$</t>
+  </si>
+  <si>
+    <t>→ hệ điều hành đã sẵn sàng cho người dùng.</t>
+  </si>
+  <si>
+    <t>🧠 5️⃣ Tóm tắt lại đúng như bạn nói</t>
+  </si>
+  <si>
+    <t>Giai đoạn</t>
+  </si>
+  <si>
+    <t>Kết quả</t>
+  </si>
+  <si>
+    <t>1️⃣ Boot ROM</t>
+  </si>
+  <si>
+    <t>Code trong SoC</t>
+  </si>
+  <si>
+    <t>Tìm &amp; load MLO (SPL)</t>
+  </si>
+  <si>
+    <t>Bắt đầu bootloader</t>
+  </si>
+  <si>
+    <t>2️⃣ U-Boot</t>
+  </si>
+  <si>
+    <t>Bootloader</t>
+  </si>
+  <si>
+    <t>Nạp kernel, dtb, rootfs; truyền bootargs</t>
+  </si>
+  <si>
+    <t>Nhảy vào kernel</t>
+  </si>
+  <si>
+    <t>3️⃣ Kernel</t>
+  </si>
+  <si>
+    <t>Nhân Linux</t>
+  </si>
+  <si>
+    <t>Khởi tạo phần cứng, tạo process 0/1</t>
+  </si>
+  <si>
+    <t>Mount rootfs</t>
+  </si>
+  <si>
+    <t>4️⃣ RootFS / User-space</t>
+  </si>
+  <si>
+    <t>/sbin/init</t>
+  </si>
+  <si>
+    <t>Khởi chạy dịch vụ, shell, ứng dụng</t>
+  </si>
+  <si>
+    <t>Người dùng thao tác được</t>
+  </si>
+  <si>
+    <t>✅ Kết luận ngắn gọn</t>
+  </si>
+  <si>
+    <t>Đúng như bạn tóm tắt:</t>
+  </si>
+  <si>
+    <t>U-Boot  →  Kernel  →  Mount RootFS  →  /sbin/init  →  User-space hoạt động</t>
+  </si>
+  <si>
+    <t>U-Boot chịu trách nhiệm nạp kernel và rootfs;</t>
+  </si>
+  <si>
+    <t>Kernel khởi tạo phần cứng + process đầu tiên;</t>
+  </si>
+  <si>
+    <t>RootFS cung cấp môi trường user-space;</t>
+  </si>
+  <si>
+    <t>Cuối cùng user mới thấy shell hoặc giao diện hệ thống.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu bạn muốn, mình có thể vẽ cho bạn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sơ đồ Boot Flow của BeagleBone</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (dạng hình mũi tên, có tên file cụ thể: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>MLO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>u-boot.img</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>zImage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>am335x-boneblack.dtb</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>rootfs.ext4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) — nhìn là hiểu toàn luồng trong 1 khung.</t>
+    </r>
+  </si>
+  <si>
+    <t>Bạn có muốn mình minh họa dạng sơ đồ đó không?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6749,14 +7959,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -6845,14 +8047,6 @@
       <name val="Cascadia Mono"/>
       <family val="3"/>
       <charset val="163"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -6957,13 +8151,47 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -7029,100 +8257,98 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7143,9 +8369,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7174,8 +8426,8 @@
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>300713</xdr:colOff>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>72113</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>35221</xdr:rowOff>
     </xdr:to>
@@ -7271,7 +8523,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>69</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
@@ -7701,15 +8953,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>334778</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>163118</xdr:rowOff>
+      <xdr:colOff>325253</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>29768</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7732,8 +8984,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647700" y="0"/>
-          <a:ext cx="10050278" cy="8545118"/>
+          <a:off x="714375" y="47625"/>
+          <a:ext cx="11269478" cy="8126018"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8007,359 +9259,359 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB039039-0D59-462A-A378-CAF13232EB1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="49"/>
+    <col min="1" max="16384" width="8.75" style="36"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="37" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="38" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="38" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="38" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="38" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="38" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="38" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
-      <c r="B4" s="51" t="s">
+    <row r="16" spans="2:2">
+      <c r="B16" s="38" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
-      <c r="B6" s="51" t="s">
+    <row r="18" spans="2:2">
+      <c r="B18" s="38" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="51" t="s">
+    <row r="20" spans="2:2">
+      <c r="B20" s="38" t="s">
         <v>507</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="51" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="51" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="51" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="51" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="51" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="51" t="s">
-        <v>513</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" location="Step!A1" display="Step" xr:uid="{1135314C-6DD4-4138-A711-BF954155A5D6}"/>
-    <hyperlink ref="B4" location="'Toolchain là gì'!A1" display="'Toolchain là gì" xr:uid="{6F874399-8D34-4430-89C2-0E5294F0FB3D}"/>
-    <hyperlink ref="B6" location="'UBoot là gì'!A1" display="'UBoot là gì'" xr:uid="{46D1502F-07C3-4E7A-B07B-8F422317BE93}"/>
-    <hyperlink ref="B8" location="'Menuconfig là gì'!A1" display="'Menuconfig là gì" xr:uid="{B4221BC8-D44A-40CD-B0FC-DBAD24BABEF5}"/>
-    <hyperlink ref="B10" location="'RootFS là gì'!A1" display="'RootFS là gì" xr:uid="{333746C9-9E34-4EFF-AFDA-8376512ED469}"/>
-    <hyperlink ref="B12" location="'Mount tập tin'!A1" display="'Mount tập tin" xr:uid="{40D24A4D-BDAE-419F-AD2B-2EBCCCED8823}"/>
-    <hyperlink ref="B14" location="'uEnv.txt là gì'!A1" display="'uEnv.txt là gì" xr:uid="{0F48E1AC-BAF7-4857-A131-6127DABFDBAC}"/>
-    <hyperlink ref="B16" location="'Sản phẩm của build Kernel'!A1" display="'Sản phẩm của build Kernel" xr:uid="{FAC02F46-83F2-4BB7-BB8E-3A6920998DDA}"/>
-    <hyperlink ref="B18" location="'File Systems Table'!A1" display="'File Systems Table" xr:uid="{4B825613-59B3-48F0-93CB-D640CF8E1496}"/>
-    <hyperlink ref="B20" location="'Cross Compiler'!A1" display="'Cross Compiler" xr:uid="{468A01D3-BF0C-493F-B59D-D83135D518DD}"/>
+    <hyperlink ref="B2" location="Step!A1" display="Step"/>
+    <hyperlink ref="B4" location="'Toolchain là gì'!A1" display="'Toolchain là gì"/>
+    <hyperlink ref="B6" location="'UBoot là gì'!A1" display="'UBoot là gì'"/>
+    <hyperlink ref="B8" location="'Menuconfig là gì'!A1" display="'Menuconfig là gì"/>
+    <hyperlink ref="B10" location="'RootFS là gì'!A1" display="'RootFS là gì"/>
+    <hyperlink ref="B12" location="'Mount tập tin'!A1" display="'Mount tập tin"/>
+    <hyperlink ref="B14" location="'uEnv.txt là gì'!A1" display="'uEnv.txt là gì"/>
+    <hyperlink ref="B16" location="'Sản phẩm của build Kernel'!A1" display="'Sản phẩm của build Kernel"/>
+    <hyperlink ref="B18" location="'File Systems Table'!A1" display="'File Systems Table"/>
+    <hyperlink ref="B20" location="'Cross Compiler'!A1" display="'Cross Compiler"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L43"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.399999999999999">
-      <c r="A1" s="7" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="36" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="17.399999999999999">
-      <c r="A3" s="7" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+    <row r="1" spans="1:12" ht="17.25">
+      <c r="A1" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15">
+      <c r="A2" s="33" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17.25">
+      <c r="A3" s="6" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15">
       <c r="A4" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15">
+      <c r="B7" s="39" t="s">
+        <v>461</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="39"/>
+    </row>
+    <row r="8" spans="1:12" ht="15">
+      <c r="B8" s="42" t="s">
+        <v>462</v>
+      </c>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="40" t="s">
+        <v>463</v>
+      </c>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="40"/>
+    </row>
+    <row r="9" spans="1:12" ht="15">
+      <c r="B9" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="40" t="s">
+        <v>465</v>
+      </c>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+    </row>
+    <row r="10" spans="1:12" ht="15">
+      <c r="B10" s="42" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="B7" s="40" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="40" t="s">
         <v>467</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="B8" s="41" t="s">
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+    </row>
+    <row r="11" spans="1:12" ht="15">
+      <c r="B11" s="42" t="s">
         <v>468</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="39" t="s">
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="40" t="s">
         <v>469</v>
       </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="41" t="s">
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+    </row>
+    <row r="12" spans="1:12" ht="15">
+      <c r="B12" s="42" t="s">
         <v>470</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="39" t="s">
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="40" t="s">
         <v>471</v>
       </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="B10" s="41" t="s">
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+    </row>
+    <row r="13" spans="1:12" ht="15">
+      <c r="B13" s="42" t="s">
         <v>472</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="39" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="40" t="s">
         <v>473</v>
       </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="B11" s="41" t="s">
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.25">
+      <c r="A15" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="39" t="s">
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="B12" s="41" t="s">
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="39" t="s">
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="B13" s="41" t="s">
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="39" t="s">
+    </row>
+    <row r="21" spans="1:1" ht="17.25">
+      <c r="A21" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-    </row>
-    <row r="15" spans="1:12" ht="17.399999999999999">
-      <c r="A15" s="7" t="s">
+    </row>
+    <row r="22" spans="1:1" ht="15">
+      <c r="A22" s="7" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="9" t="s">
+    <row r="23" spans="1:1" ht="15">
+      <c r="A23" s="34" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="9" t="s">
+    <row r="24" spans="1:1" ht="15">
+      <c r="A24" s="7" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="9" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="9" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="9" t="s">
+    <row r="26" spans="1:1" ht="15">
+      <c r="A26" s="7" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="17.399999999999999">
-      <c r="A21" s="7" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="8" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="37" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="9"/>
+    </row>
+    <row r="30" spans="1:1" ht="17.25">
+      <c r="A30" s="6" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="8" t="s">
+    <row r="31" spans="1:1" ht="15">
+      <c r="A31" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="10" t="s">
+    <row r="32" spans="1:1" ht="15">
+      <c r="A32" s="7" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="8" t="s">
+    <row r="33" spans="1:1" ht="15">
+      <c r="A33" s="7" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="10" t="s">
+    <row r="34" spans="1:1" ht="15">
+      <c r="A34" s="7"/>
+    </row>
+    <row r="35" spans="1:1" ht="17.25">
+      <c r="A35" s="6" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="10" t="s">
+    <row r="36" spans="1:1" ht="15">
+      <c r="A36" s="7" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="10"/>
-    </row>
-    <row r="30" spans="1:1" ht="17.399999999999999">
-      <c r="A30" s="7" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="9" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" s="2"/>
+    </row>
+    <row r="39" spans="1:1" ht="15">
+      <c r="A39" s="35" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="8" t="s">
+    <row r="40" spans="1:1" ht="15">
+      <c r="A40" s="9" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="8" t="s">
+    <row r="41" spans="1:1">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" spans="1:1" ht="15">
+      <c r="A42" s="7" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="8"/>
-    </row>
-    <row r="35" spans="1:1" ht="17.399999999999999">
-      <c r="A35" s="7" t="s">
+    <row r="43" spans="1:1">
+      <c r="A43" s="9" t="s">
         <v>497</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="10" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="3"/>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="38" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="10" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="8" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="10" t="s">
-        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -8384,9 +9636,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8394,424 +9646,466 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T136"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="49"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>53</v>
-      </c>
+      <c r="A1" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="B2" t="s">
-        <v>49</v>
+      <c r="B2" s="49" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="B3" t="s">
-        <v>50</v>
+      <c r="B3" s="49" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="B4" t="s">
-        <v>51</v>
+      <c r="B4" s="49" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="B6" t="s">
-        <v>52</v>
+      <c r="B6" s="49" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>54</v>
-      </c>
+      <c r="A8" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="B9" t="s">
+      <c r="B9" s="49" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="49" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="49" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="I13" s="50" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="B10" t="s">
+    <row r="14" spans="1:9">
+      <c r="B14" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="50" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="B11" t="s">
+    <row r="15" spans="1:9">
+      <c r="B15" s="49" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="56" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" t="s">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="B18" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="13" t="s">
+    </row>
+    <row r="19" spans="1:17">
+      <c r="B19" s="49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="B20" s="49" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="B22" s="49" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" t="s">
-        <v>111</v>
-      </c>
-      <c r="I14" s="13" t="s">
+      <c r="D22" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="F22" s="50" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="Q25" s="49" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="B15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
-      <c r="B18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="B19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="B20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
-      <c r="B22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" t="s">
-        <v>163</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="Q25" t="s">
-        <v>120</v>
-      </c>
-    </row>
     <row r="50" spans="1:20">
-      <c r="B50" t="s">
-        <v>162</v>
+      <c r="B50" s="49" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="1:20">
-      <c r="A52" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" ht="16.2">
-      <c r="B53" s="22" t="s">
+      <c r="A52" s="56" t="s">
+        <v>159</v>
+      </c>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+    </row>
+    <row r="53" spans="1:20" ht="16.5">
+      <c r="B53" s="20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="16.5">
+      <c r="B54" s="20" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="56"/>
+    </row>
+    <row r="57" spans="1:20">
+      <c r="B57" s="51" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" ht="15">
+      <c r="O59" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="P59" s="49" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
+      <c r="P60" s="49" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" ht="16.2">
-      <c r="B54" s="22" t="s">
+      <c r="T60" s="49" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="56" spans="1:20">
-      <c r="A56" t="s">
+    <row r="71" spans="1:8" ht="16.5">
+      <c r="B71" s="22" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="15">
-      <c r="B57" s="23" t="s">
+    <row r="72" spans="1:8" ht="16.5">
+      <c r="B72" s="22" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="59" spans="1:20">
-      <c r="O59" s="24" t="s">
+      <c r="H72" s="21" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="56" t="s">
         <v>214</v>
       </c>
-      <c r="P59" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20">
-      <c r="P60" t="s">
+      <c r="B74" s="56"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+      <c r="E74" s="56"/>
+      <c r="F74" s="56"/>
+    </row>
+    <row r="75" spans="1:8" ht="16.5">
+      <c r="B75" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="T60" t="s">
+    </row>
+    <row r="76" spans="1:8" ht="16.5">
+      <c r="B76" s="22" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="16.2">
-      <c r="B71" s="25" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="16.2">
-      <c r="B72" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="16.2">
-      <c r="B75" s="25" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="16.2">
-      <c r="B76" s="25" t="s">
-        <v>222</v>
-      </c>
-    </row>
     <row r="78" spans="1:8">
-      <c r="A78" t="s">
+      <c r="A78" s="56" t="s">
+        <v>282</v>
+      </c>
+      <c r="B78" s="56"/>
+      <c r="C78" s="56"/>
+      <c r="D78" s="56"/>
+    </row>
+    <row r="79" spans="1:8" ht="16.5">
+      <c r="B79" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="16.5">
+      <c r="B80" s="22" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="16.5">
+      <c r="B81" s="23" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="16.5">
+      <c r="B82" s="23" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="16.5">
+      <c r="B84" s="22" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" ht="16.2">
-      <c r="B79" s="25" t="s">
+      <c r="E84" s="21" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="16.5">
+      <c r="B85" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="E79" s="24" t="s">
+    </row>
+    <row r="86" spans="1:11" ht="16.5">
+      <c r="B86" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="K86" s="49" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="16.2">
-      <c r="B80" s="25" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="16.2">
-      <c r="B81" s="26" t="s">
+    <row r="88" spans="1:11" ht="16.5">
+      <c r="B88" s="24" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="16.5">
+      <c r="B89" s="22" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="16.2">
-      <c r="B82" s="26" t="s">
+    <row r="91" spans="1:11">
+      <c r="A91" s="51" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="16.5">
+      <c r="B92" s="22" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="16.5">
+      <c r="B93" s="24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="16.5">
+      <c r="B94" s="22" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="16.5">
+      <c r="B96" s="24" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="16.2">
-      <c r="B84" s="25" t="s">
-        <v>294</v>
-      </c>
-      <c r="E84" s="24" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="16.2">
-      <c r="B85" s="27" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="16.2">
-      <c r="B86" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="K86" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="16.2">
-      <c r="B88" s="27" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="16.2">
-      <c r="B89" s="25" t="s">
+    <row r="97" spans="1:11" ht="16.5">
+      <c r="B97" s="22" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="15">
-      <c r="A91" s="23" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="16.2">
-      <c r="B92" s="25" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="16.2">
-      <c r="B93" s="27" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="16.2">
-      <c r="B94" s="25" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="16.2">
-      <c r="B96" s="27" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="16.2">
-      <c r="B97" s="25" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9">
-      <c r="A99" t="s">
+    <row r="99" spans="1:11">
+      <c r="A99" s="49" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="16.5">
+      <c r="B100" s="22" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="16.5">
+      <c r="B101" s="22" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="16.5">
+      <c r="B102" s="22" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="15">
+      <c r="A104" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="B104" s="56"/>
+      <c r="C104" s="56"/>
+      <c r="D104" s="56"/>
+      <c r="E104" s="56"/>
+      <c r="F104" s="56"/>
+      <c r="G104" s="56"/>
+      <c r="H104" s="56"/>
+      <c r="I104" s="56"/>
+      <c r="J104" s="56"/>
+      <c r="K104" s="56"/>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" s="49" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="16.5">
+      <c r="B106" s="22" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="16.5">
+      <c r="B107" s="22" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="16.2">
-      <c r="B100" s="25" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="16.2">
-      <c r="B101" s="25" t="s">
+    <row r="109" spans="1:11">
+      <c r="A109" s="49" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="16.2">
-      <c r="B102" s="25" t="s">
+    <row r="110" spans="1:11">
+      <c r="B110" s="49" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="104" spans="1:9">
-      <c r="A104" s="24" t="s">
+      <c r="I110" s="49" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
-      <c r="A105" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="16.2">
-      <c r="B106" s="25" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="16.2">
-      <c r="B107" s="25" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
-      <c r="A109" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9">
-      <c r="B110" t="s">
-        <v>346</v>
-      </c>
-      <c r="I110" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9">
-      <c r="A112" t="s">
+    <row r="112" spans="1:11">
+      <c r="A112" s="49" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20" ht="16.5">
+      <c r="B113" s="26" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20">
+      <c r="A115" s="49" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" ht="16.5">
+      <c r="B116" s="26" t="s">
+        <v>380</v>
+      </c>
+      <c r="T116" s="19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" ht="16.5">
+      <c r="B117" s="26" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20">
+      <c r="A119" s="49" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20" ht="16.5">
+      <c r="B120" s="26" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="16.2">
-      <c r="B113" s="29" t="s">
+    <row r="122" spans="1:20">
+      <c r="A122" s="49" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="115" spans="1:20">
-      <c r="A115" t="s">
+    <row r="123" spans="1:20" ht="16.5">
+      <c r="B123" s="26" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="16.2">
-      <c r="B116" s="29" t="s">
+    <row r="125" spans="1:20">
+      <c r="A125" s="49" t="s">
         <v>386</v>
       </c>
-      <c r="T116" s="21" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" ht="16.2">
-      <c r="B117" s="29" t="s">
+    </row>
+    <row r="126" spans="1:20" ht="16.5">
+      <c r="B126" s="26" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="119" spans="1:20">
-      <c r="A119" t="s">
+    <row r="127" spans="1:20">
+      <c r="B127" s="49" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="16.2">
-      <c r="B120" s="29" t="s">
+    <row r="128" spans="1:20" ht="16.5">
+      <c r="C128" s="27" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="122" spans="1:20">
-      <c r="A122" t="s">
+    <row r="129" spans="1:3" ht="16.5">
+      <c r="C129" s="27" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="16.2">
-      <c r="B123" s="29" t="s">
+    <row r="131" spans="1:3" ht="16.5">
+      <c r="C131" s="27" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="125" spans="1:20">
-      <c r="A125" t="s">
+    <row r="132" spans="1:3" ht="16.5">
+      <c r="C132" s="27" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="16.2">
-      <c r="B126" s="29" t="s">
+    <row r="134" spans="1:3">
+      <c r="A134" s="49" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="127" spans="1:20">
-      <c r="B127" t="s">
+    <row r="135" spans="1:3" ht="16.5">
+      <c r="B135" s="26" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="16.5">
+      <c r="B136" s="26" t="s">
         <v>394</v>
-      </c>
-    </row>
-    <row r="128" spans="1:20" ht="16.2">
-      <c r="C128" s="30" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="16.2">
-      <c r="C129" s="30" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="16.2">
-      <c r="C131" s="30" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="16.2">
-      <c r="C132" s="30" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
-      <c r="A134" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="16.2">
-      <c r="B135" s="29" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="16.2">
-      <c r="B136" s="29" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -8822,341 +10116,326 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="49"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:10" ht="15">
+      <c r="B2" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="B3" s="53" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:10">
+      <c r="B4" s="53" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:10">
+      <c r="B5" s="53" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:10" ht="15">
+      <c r="B6" s="53" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="3" t="s">
+    <row r="8" spans="1:10" ht="15">
+      <c r="B8" s="49" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="52" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
+    <row r="12" spans="1:10" ht="15">
+      <c r="B12" s="39" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" t="s">
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="30">
-      <c r="A10" s="1" t="s">
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+    </row>
+    <row r="13" spans="1:10" ht="15">
+      <c r="B13" s="42" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="40" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40" t="s">
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+    </row>
+    <row r="14" spans="1:10" ht="15">
+      <c r="B14" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="41" t="s">
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="39" t="s">
+      <c r="F14" s="54"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+    </row>
+    <row r="15" spans="1:10" ht="15">
+      <c r="B15" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="41" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="39" t="s">
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
+    </row>
+    <row r="16" spans="1:10" ht="15">
+      <c r="B16" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="41" t="s">
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="39" t="s">
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="54"/>
+      <c r="J16" s="54"/>
+    </row>
+    <row r="17" spans="1:10" ht="15">
+      <c r="B17" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="41" t="s">
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="39" t="s">
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="54"/>
+    </row>
+    <row r="18" spans="1:10" ht="15">
+      <c r="B18" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="B17" s="41" t="s">
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="39" t="s">
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54"/>
+      <c r="J18" s="54"/>
+    </row>
+    <row r="20" spans="1:10" ht="15">
+      <c r="A20" s="49" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15">
+      <c r="A22" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="B18" s="41" t="s">
+    </row>
+    <row r="23" spans="1:10" ht="15">
+      <c r="B23" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="39" t="s">
+      <c r="C23" s="39"/>
+      <c r="D23" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="39"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="B24" s="54" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="30">
-      <c r="A22" s="1" t="s">
+      <c r="C24" s="54"/>
+      <c r="D24" s="55" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="B23" s="40" t="s">
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="B25" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40" t="s">
+      <c r="C25" s="54"/>
+      <c r="D25" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="B24" s="39" t="s">
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="B26" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="42" t="s">
+      <c r="C26" s="54"/>
+      <c r="D26" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="B25" s="39" t="s">
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="B27" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="42" t="s">
+      <c r="C27" s="54"/>
+      <c r="D27" s="55" t="s">
+        <v>512</v>
+      </c>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+    </row>
+    <row r="30" spans="1:10" ht="15">
+      <c r="A30" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="B26" s="39" t="s">
+    </row>
+    <row r="31" spans="1:10">
+      <c r="B31" s="53" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="B32" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="42" t="s">
+    </row>
+    <row r="33" spans="1:9">
+      <c r="B33" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="B27" s="39" t="s">
+    </row>
+    <row r="34" spans="1:9">
+      <c r="B34" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="42" t="s">
+    </row>
+    <row r="36" spans="1:9" ht="15">
+      <c r="A36" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-    </row>
-    <row r="30" spans="1:10" ht="30">
-      <c r="A30" s="1" t="s">
+    </row>
+    <row r="38" spans="1:9" ht="15">
+      <c r="B38" s="39" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="B31" s="3" t="s">
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="B32" s="3" t="s">
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="B39" s="54" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="B33" s="3" t="s">
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="B34" s="3" t="s">
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="B40" s="54" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="30">
-      <c r="A36" s="1" t="s">
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="B38" s="40" t="s">
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="54"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="B41" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40" t="s">
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="B39" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-    </row>
-    <row r="40" spans="1:9" ht="29.25" customHeight="1">
-      <c r="B40" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="B41" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
+      <c r="F41" s="54"/>
+      <c r="G41" s="54"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="E40:I40"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
     <mergeCell ref="E18:J18"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B13:D13"/>
@@ -9171,6 +10450,24 @@
     <mergeCell ref="E15:J15"/>
     <mergeCell ref="E16:J16"/>
     <mergeCell ref="E17:J17"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E38:I38"/>
+    <mergeCell ref="E39:I39"/>
+    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="E41:I41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9178,680 +10475,668 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U87"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="15.8984375" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.399999999999999">
-      <c r="A1" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="12" t="s">
-        <v>105</v>
+    <row r="1" spans="1:3" ht="17.25">
+      <c r="A1" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15">
+      <c r="A2" s="11" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.399999999999999">
-      <c r="A7" s="7" t="s">
-        <v>59</v>
+      <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15">
+      <c r="A4" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.25">
+      <c r="A7" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="C13" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="C14" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="B9" s="11" t="s">
+    <row r="15" spans="1:3">
+      <c r="C15" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="B10" s="3" t="s">
+    <row r="17" spans="1:14" ht="17.25">
+      <c r="A17" s="6" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="B11" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="B12" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="C13" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="C14" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="C15" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="17.399999999999999">
-      <c r="A17" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15">
+      <c r="A19" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15">
+      <c r="A20" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="17.25">
+      <c r="A22" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15">
+      <c r="A23" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15">
+      <c r="A24" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15">
+      <c r="A25" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="8" t="s">
+    <row r="26" spans="1:14" ht="15">
+      <c r="A26" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="8" t="s">
+    <row r="27" spans="1:14" ht="15">
+      <c r="A27" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.399999999999999">
-      <c r="A22" s="7" t="s">
+    <row r="29" spans="1:14" ht="17.25">
+      <c r="A29" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="8" t="s">
+    <row r="31" spans="1:14" ht="15">
+      <c r="B31" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="8" t="s">
+      <c r="C31" s="39" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="8" t="s">
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="N31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="23.25">
+      <c r="B32" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="8" t="s">
+      <c r="C32" s="40" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="8" t="s">
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="N32" s="18" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="17.25">
+      <c r="B33" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="17.399999999999999">
-      <c r="A29" s="7" t="s">
+      <c r="C33" s="40" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="B31" s="5" t="s">
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="N33" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15">
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="40" t="s">
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="N34" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="17.25">
+      <c r="B35" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="N31" t="s">
+      <c r="C35" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="N35" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15">
+      <c r="N36" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
+      <c r="N37" s="9" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="22.8">
-      <c r="B32" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="39" t="s">
+    <row r="38" spans="1:20" ht="15">
+      <c r="A38" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
+      <c r="B39" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="N32" s="20" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="17.399999999999999">
-      <c r="B33" s="6" t="s">
+      <c r="N39" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="17.25">
+      <c r="B40" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="39" t="s">
+      <c r="N40" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15">
+      <c r="B41" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="N33" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="B34" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="N34" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="17.399999999999999">
-      <c r="B35" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="N35" s="7" t="s">
+      <c r="O41" s="46" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="N36" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="N37" s="10" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20">
-      <c r="A38" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="N38" s="10" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20">
-      <c r="B39" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" ht="17.399999999999999">
-      <c r="B40" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N40" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20">
-      <c r="B41" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="O41" s="46" t="s">
-        <v>233</v>
       </c>
       <c r="P41" s="47"/>
       <c r="Q41" s="46" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="R41" s="48"/>
       <c r="S41" s="48"/>
       <c r="T41" s="47"/>
     </row>
     <row r="42" spans="1:20">
-      <c r="B42" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N42" s="3"/>
+      <c r="B42" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="43" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P42" s="45"/>
       <c r="Q42" s="43" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="R42" s="44"/>
       <c r="S42" s="44"/>
       <c r="T42" s="45"/>
     </row>
     <row r="43" spans="1:20">
-      <c r="B43" s="9" t="s">
-        <v>91</v>
+      <c r="B43" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="O43" s="43" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="P43" s="45"/>
       <c r="Q43" s="43" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="R43" s="44"/>
       <c r="S43" s="44"/>
       <c r="T43" s="45"/>
     </row>
     <row r="44" spans="1:20">
-      <c r="B44" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N44" s="3"/>
+      <c r="B44" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="43" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="P44" s="45"/>
       <c r="Q44" s="43" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="R44" s="44"/>
       <c r="S44" s="44"/>
       <c r="T44" s="45"/>
     </row>
     <row r="45" spans="1:20">
-      <c r="B45" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N45" s="3"/>
+      <c r="B45" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="43" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="P45" s="45"/>
       <c r="Q45" s="43" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="R45" s="44"/>
       <c r="S45" s="44"/>
       <c r="T45" s="45"/>
     </row>
     <row r="46" spans="1:20">
-      <c r="B46" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N46" s="10"/>
+      <c r="B46" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N46" s="9"/>
       <c r="O46" s="43" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="P46" s="45"/>
       <c r="Q46" s="43" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="R46" s="44"/>
       <c r="S46" s="44"/>
       <c r="T46" s="45"/>
     </row>
     <row r="47" spans="1:20">
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15">
+      <c r="B48" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
+      <c r="B49" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="14.25" customHeight="1">
+      <c r="B50" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N50" s="18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="14.25" customHeight="1">
+      <c r="B51" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="14.25" customHeight="1">
+      <c r="B52" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="14.25" customHeight="1">
+      <c r="B53" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="14.25" customHeight="1">
+      <c r="B54" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N54" s="9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
+      <c r="B55" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
+      <c r="B56" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
+      <c r="B57" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="N57" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="17.25">
+      <c r="A59" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="B48" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21">
-      <c r="B49" s="9" t="s">
+      <c r="N59" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="15">
+      <c r="A60" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="14.25" customHeight="1">
-      <c r="B50" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N50" s="20" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" ht="14.25" customHeight="1">
-      <c r="B51" s="9" t="s">
+    <row r="61" spans="1:21" ht="15">
+      <c r="A61" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" ht="14.25" customHeight="1">
-      <c r="B52" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N52" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="14.25" customHeight="1">
-      <c r="B53" s="9" t="s">
+      <c r="O61" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="P61" s="39"/>
+      <c r="Q61" s="39"/>
+      <c r="R61" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="S61" s="39"/>
+      <c r="T61" s="39"/>
+      <c r="U61" s="39"/>
+    </row>
+    <row r="62" spans="1:21" ht="15">
+      <c r="A62" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="N53" s="3" t="s">
+      <c r="O62" s="40" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" ht="14.25" customHeight="1">
-      <c r="B54" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N54" s="10" t="s">
+      <c r="P62" s="40"/>
+      <c r="Q62" s="40"/>
+      <c r="R62" s="40" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="55" spans="1:21">
-      <c r="B55" s="9" t="s">
+      <c r="S62" s="40"/>
+      <c r="T62" s="40"/>
+      <c r="U62" s="40"/>
+    </row>
+    <row r="63" spans="1:21" ht="15">
+      <c r="A63" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="N55" s="10" t="s">
+      <c r="O63" s="40" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="56" spans="1:21">
-      <c r="B56" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="N56" s="10" t="s">
+      <c r="P63" s="40"/>
+      <c r="Q63" s="40"/>
+      <c r="R63" s="40" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="57" spans="1:21">
-      <c r="B57" s="9" t="s">
+      <c r="S63" s="40"/>
+      <c r="T63" s="40"/>
+      <c r="U63" s="40"/>
+    </row>
+    <row r="64" spans="1:21" ht="15">
+      <c r="A64" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="N57" s="10" t="s">
+      <c r="O64" s="40" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" ht="17.399999999999999">
-      <c r="A59" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N59" s="7" t="s">
+      <c r="P64" s="40"/>
+      <c r="Q64" s="40"/>
+      <c r="R64" s="40" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="60" spans="1:21">
-      <c r="A60" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21">
-      <c r="A61" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="O61" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="P61" s="40"/>
-      <c r="Q61" s="40"/>
-      <c r="R61" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="S61" s="40"/>
-      <c r="T61" s="40"/>
-      <c r="U61" s="40"/>
-    </row>
-    <row r="62" spans="1:21">
-      <c r="A62" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="O62" s="39" t="s">
+      <c r="S64" s="40"/>
+      <c r="T64" s="40"/>
+      <c r="U64" s="40"/>
+    </row>
+    <row r="65" spans="1:21">
+      <c r="O65" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="P62" s="39"/>
-      <c r="Q62" s="39"/>
-      <c r="R62" s="39" t="s">
+      <c r="P65" s="40"/>
+      <c r="Q65" s="40"/>
+      <c r="R65" s="40" t="s">
         <v>253</v>
       </c>
-      <c r="S62" s="39"/>
-      <c r="T62" s="39"/>
-      <c r="U62" s="39"/>
-    </row>
-    <row r="63" spans="1:21">
-      <c r="A63" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="O63" s="39" t="s">
+      <c r="S65" s="40"/>
+      <c r="T65" s="40"/>
+      <c r="U65" s="40"/>
+    </row>
+    <row r="66" spans="1:21">
+      <c r="O66" s="40" t="s">
         <v>254</v>
       </c>
-      <c r="P63" s="39"/>
-      <c r="Q63" s="39"/>
-      <c r="R63" s="39" t="s">
+      <c r="P66" s="40"/>
+      <c r="Q66" s="40"/>
+      <c r="R66" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="S63" s="39"/>
-      <c r="T63" s="39"/>
-      <c r="U63" s="39"/>
-    </row>
-    <row r="64" spans="1:21">
-      <c r="A64" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="O64" s="39" t="s">
+      <c r="S66" s="41"/>
+      <c r="T66" s="41"/>
+      <c r="U66" s="41"/>
+    </row>
+    <row r="67" spans="1:21">
+      <c r="O67" s="40" t="s">
         <v>256</v>
       </c>
-      <c r="P64" s="39"/>
-      <c r="Q64" s="39"/>
-      <c r="R64" s="39" t="s">
+      <c r="P67" s="40"/>
+      <c r="Q67" s="40"/>
+      <c r="R67" s="40" t="s">
         <v>257</v>
       </c>
-      <c r="S64" s="39"/>
-      <c r="T64" s="39"/>
-      <c r="U64" s="39"/>
-    </row>
-    <row r="65" spans="1:21">
-      <c r="O65" s="39" t="s">
+      <c r="S67" s="40"/>
+      <c r="T67" s="40"/>
+      <c r="U67" s="40"/>
+    </row>
+    <row r="68" spans="1:21" ht="23.25">
+      <c r="A68" s="16" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="23.25">
+      <c r="A69" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="N69" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="P65" s="39"/>
-      <c r="Q65" s="39"/>
-      <c r="R65" s="39" t="s">
+    </row>
+    <row r="70" spans="1:21" ht="15">
+      <c r="A70" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="O70" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="S65" s="39"/>
-      <c r="T65" s="39"/>
-      <c r="U65" s="39"/>
-    </row>
-    <row r="66" spans="1:21">
-      <c r="O66" s="39" t="s">
+    </row>
+    <row r="71" spans="1:21" ht="15">
+      <c r="A71" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="O71" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="P66" s="39"/>
-      <c r="Q66" s="39"/>
-      <c r="R66" s="42" t="s">
+    </row>
+    <row r="72" spans="1:21">
+      <c r="A72" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="O72" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="S66" s="42"/>
-      <c r="T66" s="42"/>
-      <c r="U66" s="42"/>
-    </row>
-    <row r="67" spans="1:21">
-      <c r="O67" s="39" t="s">
+    </row>
+    <row r="73" spans="1:21">
+      <c r="O73" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="P67" s="39"/>
-      <c r="Q67" s="39"/>
-      <c r="R67" s="39" t="s">
+    </row>
+    <row r="74" spans="1:21" ht="15">
+      <c r="A74" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="O74" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="S67" s="39"/>
-      <c r="T67" s="39"/>
-      <c r="U67" s="39"/>
-    </row>
-    <row r="68" spans="1:21" ht="22.8">
-      <c r="A68" s="18" t="s">
+    </row>
+    <row r="75" spans="1:21">
+      <c r="A75" s="9" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" ht="22.8">
-      <c r="A69" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="N69" s="20" t="s">
+      <c r="O75" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
+      <c r="O76" s="8" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="70" spans="1:21">
-      <c r="A70" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="O70" s="9" t="s">
+    <row r="77" spans="1:21">
+      <c r="A77" s="2"/>
+      <c r="O77" s="8" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="71" spans="1:21">
-      <c r="A71" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="O71" s="9" t="s">
+    <row r="78" spans="1:21">
+      <c r="A78" s="9"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="8" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="72" spans="1:21">
-      <c r="A72" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="O72" s="9" t="s">
+    <row r="79" spans="1:21">
+      <c r="N79" s="8"/>
+      <c r="O79" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
+      <c r="N80" s="8"/>
+      <c r="O80" s="8" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="73" spans="1:21">
-      <c r="O73" s="9" t="s">
+    <row r="81" spans="14:17">
+      <c r="O81" s="8" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="74" spans="1:21">
-      <c r="A74" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="O74" s="9" t="s">
+    <row r="83" spans="14:17" ht="23.25">
+      <c r="N83" s="18" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="75" spans="1:21">
-      <c r="A75" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21">
-      <c r="O76" s="9" t="s">
+    <row r="85" spans="14:17" ht="15">
+      <c r="O85" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="P85" s="39"/>
+      <c r="Q85" s="4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="77" spans="1:21">
-      <c r="A77" s="3"/>
-      <c r="O77" s="9" t="s">
+    <row r="86" spans="14:17">
+      <c r="O86" s="40" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="78" spans="1:21">
-      <c r="A78" s="10"/>
-      <c r="N78" s="15"/>
-      <c r="O78" s="9" t="s">
+      <c r="P86" s="40"/>
+      <c r="Q86" s="17" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="79" spans="1:21">
-      <c r="N79" s="9"/>
-      <c r="O79" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21">
-      <c r="N80" s="9"/>
-      <c r="O80" s="9" t="s">
+    <row r="87" spans="14:17">
+      <c r="O87" s="40" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="81" spans="14:17">
-      <c r="O81" s="9" t="s">
+      <c r="P87" s="40"/>
+      <c r="Q87" s="17" t="s">
         <v>274</v>
-      </c>
-    </row>
-    <row r="83" spans="14:17" ht="22.8">
-      <c r="N83" s="20" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="85" spans="14:17">
-      <c r="O85" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="P85" s="40"/>
-      <c r="Q85" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="86" spans="14:17">
-      <c r="O86" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="P86" s="39"/>
-      <c r="Q86" s="19" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="87" spans="14:17">
-      <c r="O87" s="39" t="s">
-        <v>279</v>
-      </c>
-      <c r="P87" s="39"/>
-      <c r="Q87" s="19" t="s">
-        <v>280</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="O85:P85"/>
-    <mergeCell ref="O86:P86"/>
-    <mergeCell ref="O87:P87"/>
-    <mergeCell ref="R66:U66"/>
-    <mergeCell ref="R67:U67"/>
-    <mergeCell ref="O61:Q61"/>
-    <mergeCell ref="O62:Q62"/>
-    <mergeCell ref="O63:Q63"/>
-    <mergeCell ref="O64:Q64"/>
-    <mergeCell ref="O65:Q65"/>
-    <mergeCell ref="R61:U61"/>
-    <mergeCell ref="R62:U62"/>
-    <mergeCell ref="R63:U63"/>
-    <mergeCell ref="R64:U64"/>
-    <mergeCell ref="R65:U65"/>
-    <mergeCell ref="O66:Q66"/>
-    <mergeCell ref="O67:Q67"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
     <mergeCell ref="Q46:T46"/>
     <mergeCell ref="O41:P41"/>
     <mergeCell ref="O42:P42"/>
@@ -9864,11 +11149,23 @@
     <mergeCell ref="Q43:T43"/>
     <mergeCell ref="Q44:T44"/>
     <mergeCell ref="Q45:T45"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="R61:U61"/>
+    <mergeCell ref="R62:U62"/>
+    <mergeCell ref="R63:U63"/>
+    <mergeCell ref="R64:U64"/>
+    <mergeCell ref="R65:U65"/>
+    <mergeCell ref="O61:Q61"/>
+    <mergeCell ref="O62:Q62"/>
+    <mergeCell ref="O63:Q63"/>
+    <mergeCell ref="O64:Q64"/>
+    <mergeCell ref="O65:Q65"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="O86:P86"/>
+    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="R66:U66"/>
+    <mergeCell ref="R67:U67"/>
+    <mergeCell ref="O66:Q66"/>
+    <mergeCell ref="O67:Q67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9877,229 +11174,229 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:2" ht="15">
+      <c r="A1" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15">
+      <c r="A2" s="7"/>
+    </row>
+    <row r="3" spans="1:2" ht="17.25">
+      <c r="A3" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15">
+      <c r="A4" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15">
+      <c r="A6" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="B7" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15">
+      <c r="A8" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="8"/>
-    </row>
-    <row r="3" spans="1:2" ht="17.399999999999999">
-      <c r="A3" s="7" t="s">
+    <row r="9" spans="1:2">
+      <c r="B9" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+    <row r="10" spans="1:2" ht="15">
+      <c r="A10" s="2" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="B5" s="3" t="s">
+    <row r="11" spans="1:2">
+      <c r="B11" s="2" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
+    <row r="12" spans="1:2" ht="15">
+      <c r="A12" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="B7" s="3" t="s">
+    <row r="13" spans="1:2">
+      <c r="B13" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="3" t="s">
+    <row r="14" spans="1:2" ht="15">
+      <c r="A14" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="B9" s="3" t="s">
+    <row r="15" spans="1:2" ht="15">
+      <c r="B15" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
+    <row r="16" spans="1:2" ht="15">
+      <c r="B16" s="12" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="B11" s="3" t="s">
+    <row r="17" spans="1:8" ht="15">
+      <c r="B17" s="12" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="3" t="s">
+    <row r="18" spans="1:8" ht="15">
+      <c r="A18" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="B13" s="3" t="s">
+    <row r="19" spans="1:8">
+      <c r="B19" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="3" t="s">
+    <row r="21" spans="1:8" ht="23.25">
+      <c r="A21" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="H21" s="15" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="B15" s="14" t="s">
+    <row r="23" spans="1:8" ht="17.25">
+      <c r="A23" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="B16" s="14" t="s">
+    <row r="24" spans="1:8" ht="15">
+      <c r="B24" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="B17" s="14" t="s">
+    <row r="25" spans="1:8" ht="15">
+      <c r="B25" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="3" t="s">
+    <row r="27" spans="1:8" ht="17.25">
+      <c r="A27" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="B19" s="3" t="s">
+    <row r="28" spans="1:8">
+      <c r="A28" s="13"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="B29" s="8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="22.8">
-      <c r="A21" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="H21" s="17" t="s">
+    <row r="30" spans="1:8">
+      <c r="B30" s="8" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="17.399999999999999">
-      <c r="A23" s="7" t="s">
+    <row r="31" spans="1:8">
+      <c r="B31" s="8" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="B24" s="3" t="s">
+    <row r="32" spans="1:8">
+      <c r="B32" s="8" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="B25" s="3" t="s">
+    <row r="33" spans="1:6">
+      <c r="B33" s="8" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="17.399999999999999">
-      <c r="A27" s="7" t="s">
+    <row r="34" spans="1:6">
+      <c r="B34" s="8" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="15"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="B29" s="9" t="s">
+    <row r="35" spans="1:6">
+      <c r="A35" s="14"/>
+    </row>
+    <row r="36" spans="1:6" ht="15">
+      <c r="B36" s="39" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="B30" s="9" t="s">
+      <c r="C36" s="39"/>
+      <c r="D36" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="B37" s="41" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="B31" s="9" t="s">
+      <c r="C37" s="41"/>
+      <c r="D37" s="40" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="B32" s="9" t="s">
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="B38" s="41" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="B33" s="9" t="s">
+      <c r="C38" s="41"/>
+      <c r="D38" s="40" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="B34" s="9" t="s">
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="41" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="16"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="B36" s="40" t="s">
+      <c r="C39" s="41"/>
+      <c r="D39" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="B37" s="42" t="s">
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+    </row>
+    <row r="41" spans="1:6" ht="17.25">
+      <c r="A41" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="39" t="s">
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="B38" s="42" t="s">
+    </row>
+    <row r="43" spans="1:6">
+      <c r="B43" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="39" t="s">
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="B39" s="42" t="s">
-        <v>155</v>
-      </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-    </row>
-    <row r="41" spans="1:6" ht="17.399999999999999">
-      <c r="A41" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="B42" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="B43" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="B44" s="3" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -10118,267 +11415,733 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I171"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.8">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:9" ht="23.25">
+      <c r="A1" s="18" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15">
+      <c r="A3" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15">
+      <c r="B5" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="I5" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15">
+      <c r="B6" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="41"/>
+      <c r="D6" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="I6" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15">
+      <c r="B7" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="41"/>
+      <c r="D7" s="40" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="I7" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8" s="41" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" s="40" t="s">
+      <c r="C8" s="41"/>
+      <c r="D8" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" s="42" t="s">
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="39" t="s">
+      <c r="C9" s="41"/>
+      <c r="D9" s="40" t="s">
         <v>170</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" s="42" t="s">
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="39" t="s">
+      <c r="C10" s="41"/>
+      <c r="D10" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8" s="42" t="s">
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="39" t="s">
+      <c r="C11" s="41"/>
+      <c r="D11" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="B9" s="42" t="s">
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+    </row>
+    <row r="14" spans="1:9" ht="23.25">
+      <c r="A14" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="39" t="s">
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" ht="15">
+      <c r="B16" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" s="42" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="15">
+      <c r="B17" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="39" t="s">
+    </row>
+    <row r="18" spans="1:7" ht="15">
+      <c r="B18" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11" s="42" t="s">
+    </row>
+    <row r="19" spans="1:7" ht="15">
+      <c r="B19" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="39" t="s">
+    </row>
+    <row r="20" spans="1:7" ht="15">
+      <c r="A20" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="23.25">
+      <c r="A22" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-    </row>
-    <row r="14" spans="1:7" ht="22.8">
-      <c r="A14" s="20" t="s">
+    </row>
+    <row r="23" spans="1:7" ht="15">
+      <c r="B23" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="3"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="8" t="s">
+    <row r="24" spans="1:7" ht="15">
+      <c r="B24" s="7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="B17" s="8" t="s">
+    <row r="25" spans="1:7" ht="15">
+      <c r="B25" s="7" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="B18" s="8" t="s">
+    <row r="26" spans="1:7" ht="15">
+      <c r="B26" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="B19" s="8" t="s">
+    <row r="27" spans="1:7" ht="15">
+      <c r="B27" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="21" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="22.8">
-      <c r="A22" s="20" t="s">
+    <row r="29" spans="1:7" ht="23.25">
+      <c r="A29" s="18" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="B23" t="s">
+    <row r="31" spans="1:7" ht="15">
+      <c r="B31" s="39" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="B24" s="8" t="s">
+      <c r="C31" s="39"/>
+      <c r="D31" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+    </row>
+    <row r="32" spans="1:7" ht="15">
+      <c r="B32" s="42" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="B25" s="8" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="40" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="B26" s="8" t="s">
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+    </row>
+    <row r="33" spans="1:7" ht="15">
+      <c r="B33" s="42" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="B27" s="8" t="s">
+      <c r="C33" s="42"/>
+      <c r="D33" s="40" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="22.8">
-      <c r="A29" s="20" t="s">
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+    </row>
+    <row r="34" spans="1:7" ht="15">
+      <c r="B34" s="42" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="B31" s="40" t="s">
+      <c r="C34" s="42"/>
+      <c r="D34" s="40" t="s">
         <v>193</v>
       </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="B32" s="41" t="s">
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+    </row>
+    <row r="35" spans="1:7" ht="15">
+      <c r="B35" s="42" t="s">
         <v>194</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="39" t="s">
+      <c r="C35" s="42"/>
+      <c r="D35" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="B33" s="41" t="s">
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+    </row>
+    <row r="38" spans="1:7" ht="23.25">
+      <c r="A38" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="39" t="s">
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" ht="15">
+      <c r="B40" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="B34" s="41" t="s">
+    </row>
+    <row r="41" spans="1:7">
+      <c r="B41" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="B35" s="41" t="s">
-        <v>200</v>
-      </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="39" t="s">
-        <v>201</v>
-      </c>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-    </row>
-    <row r="38" spans="1:7" ht="22.8">
-      <c r="A38" s="20" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="3"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="B40" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="B41" s="3" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="B42" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="B43" s="9" t="s">
-        <v>206</v>
+      <c r="B43" s="8" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="B45" t="s">
-        <v>207</v>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="23.25">
+      <c r="A47" s="18" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="8" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="8" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="8" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="8" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="8" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="23.25">
+      <c r="A58" s="18" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="17.25">
+      <c r="A60" s="6" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2"/>
+    </row>
+    <row r="62" spans="1:1" ht="15">
+      <c r="A62" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="2"/>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="2"/>
+    </row>
+    <row r="66" spans="1:1" ht="15">
+      <c r="A66" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="17.25">
+      <c r="A72" s="6" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="2"/>
+    </row>
+    <row r="74" spans="1:1" ht="15">
+      <c r="A74" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="2"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="2"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="2"/>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="9"/>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="9" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="9"/>
+    </row>
+    <row r="82" spans="1:1" ht="15">
+      <c r="A82" s="9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="15">
+      <c r="A83" s="12" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="15">
+      <c r="A84" s="9" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="9"/>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="9" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="9"/>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="34" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="9"/>
+    </row>
+    <row r="90" spans="1:1" ht="15">
+      <c r="A90" s="9" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="17.25">
+      <c r="A96" s="6" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="2"/>
+    </row>
+    <row r="100" spans="1:1" ht="15">
+      <c r="A100" s="7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="2"/>
+    </row>
+    <row r="102" spans="1:1" ht="15">
+      <c r="A102" s="7" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="2"/>
+    </row>
+    <row r="104" spans="1:1" ht="15">
+      <c r="A104" s="7" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="2"/>
+    </row>
+    <row r="106" spans="1:1" ht="15">
+      <c r="A106" s="7" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="2"/>
+    </row>
+    <row r="108" spans="1:1" ht="15">
+      <c r="A108" s="7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="2"/>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="25" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="8" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="17.25">
+      <c r="A118" s="6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="2"/>
+    </row>
+    <row r="122" spans="1:1" ht="15">
+      <c r="A122" s="7" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="2"/>
+    </row>
+    <row r="124" spans="1:1" ht="15">
+      <c r="A124" s="7" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="2"/>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="25" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="2"/>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="2"/>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="9"/>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="9" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="9"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="9"/>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="58"/>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="58" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="58"/>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="58" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="58"/>
+    </row>
+    <row r="138" spans="1:1" ht="15">
+      <c r="A138" s="58" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="8" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="23.25">
+      <c r="A148" s="18" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="30">
+      <c r="A150" s="59" t="s">
+        <v>564</v>
+      </c>
+      <c r="B150" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="D150" s="59" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="57">
+      <c r="A151" s="60" t="s">
+        <v>566</v>
+      </c>
+      <c r="B151" s="60" t="s">
+        <v>567</v>
+      </c>
+      <c r="C151" s="60" t="s">
+        <v>568</v>
+      </c>
+      <c r="D151" s="60" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="85.5">
+      <c r="A152" s="60" t="s">
+        <v>570</v>
+      </c>
+      <c r="B152" s="60" t="s">
+        <v>571</v>
+      </c>
+      <c r="C152" s="60" t="s">
+        <v>572</v>
+      </c>
+      <c r="D152" s="60" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="85.5">
+      <c r="A153" s="60" t="s">
+        <v>574</v>
+      </c>
+      <c r="B153" s="60" t="s">
+        <v>575</v>
+      </c>
+      <c r="C153" s="60" t="s">
+        <v>576</v>
+      </c>
+      <c r="D153" s="60" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="71.25">
+      <c r="A154" s="60" t="s">
+        <v>578</v>
+      </c>
+      <c r="B154" s="61" t="s">
+        <v>579</v>
+      </c>
+      <c r="C154" s="60" t="s">
+        <v>580</v>
+      </c>
+      <c r="D154" s="60" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="23.25">
+      <c r="A157" s="18" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="2"/>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="2"/>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="25" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="2"/>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="15">
+      <c r="A170" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
@@ -10393,198 +12156,189 @@
     <mergeCell ref="D8:G8"/>
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="D10:G10"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="22.8">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:2" ht="23.25">
+      <c r="A1" s="18" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15">
+      <c r="B2" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="23.25">
+      <c r="A3" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.25">
+      <c r="A4" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="8" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.25">
+      <c r="A7" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="2"/>
+      <c r="B8" s="25" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="B2" s="8" t="s">
+    <row r="9" spans="1:2">
+      <c r="B9" s="25" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="22.8">
-      <c r="A3" s="20" t="s">
+    <row r="10" spans="1:2">
+      <c r="B10" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="17.399999999999999">
-      <c r="A4" s="7" t="s">
+    <row r="12" spans="1:2" ht="23.25">
+      <c r="A12" s="18" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="15"/>
-      <c r="B5" s="9" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="17.399999999999999">
-      <c r="A7" s="7" t="s">
+    <row r="14" spans="1:2">
+      <c r="B14" s="8" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="28" t="s">
+    <row r="16" spans="1:2" ht="23.25">
+      <c r="A16" s="18" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="B9" s="28" t="s">
+    <row r="18" spans="1:6" ht="15">
+      <c r="B18" s="39" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="B10" s="3" t="s">
+      <c r="C18" s="39"/>
+      <c r="D18" s="39" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="22.8">
-      <c r="A12" s="20" t="s">
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="B19" s="40" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
+      <c r="C19" s="40"/>
+      <c r="D19" s="41" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="B14" s="9" t="s">
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="40" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="22.8">
-      <c r="A16" s="20" t="s">
+      <c r="C20" s="40"/>
+      <c r="D20" s="40" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="40" t="s">
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40" t="s">
+      <c r="C21" s="40"/>
+      <c r="D21" s="41" t="s">
         <v>318</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="39" t="s">
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="40" t="s">
         <v>319</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="42" t="s">
+      <c r="C22" s="40"/>
+      <c r="D22" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="39" t="s">
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39" t="s">
+      <c r="C23" s="40"/>
+      <c r="D23" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="39" t="s">
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+    </row>
+    <row r="25" spans="1:6" ht="23.25">
+      <c r="A25" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="42" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="B26" t="s">
         <v>324</v>
       </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="39" t="s">
+    </row>
+    <row r="27" spans="1:6">
+      <c r="B27" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39" t="s">
+    </row>
+    <row r="28" spans="1:6">
+      <c r="B28" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="39" t="s">
+    </row>
+    <row r="29" spans="1:6">
+      <c r="B29" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="C23" s="39"/>
-      <c r="D23" s="42" t="s">
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="25" t="s">
         <v>328</v>
-      </c>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-    </row>
-    <row r="25" spans="1:6" ht="22.8">
-      <c r="A25" s="20" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="B27" s="28" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="28" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="28" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="B31" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="B32" s="9" t="s">
-        <v>336</v>
+      <c r="B32" s="8" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -10607,193 +12361,193 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="22.8">
-      <c r="A1" s="18" t="s">
-        <v>401</v>
+    <row r="1" spans="1:2" ht="23.25">
+      <c r="A1" s="16" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="8" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="8" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="8" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15">
+      <c r="A3" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15">
+      <c r="A4" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15">
+      <c r="A5" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15">
       <c r="A6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="21" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="22.8">
-      <c r="A9" s="20" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15">
+      <c r="A8" s="19" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="23.25">
+      <c r="A9" s="18" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15">
+      <c r="A10" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="B12" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="B13" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="B14" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="B15" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
+    <row r="16" spans="1:2">
+      <c r="B16" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="B11" s="3" t="s">
+    <row r="18" spans="1:2" ht="23.25">
+      <c r="A18" s="18" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="B12" s="3" t="s">
+    <row r="19" spans="1:2">
+      <c r="B19" s="8" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="B13" s="3" t="s">
+    <row r="20" spans="1:2">
+      <c r="B20" s="8" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="B14" s="3" t="s">
+    <row r="21" spans="1:2">
+      <c r="B21" s="8" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="B15" s="3" t="s">
+    <row r="22" spans="1:2">
+      <c r="B22" s="8" t="s">
         <v>354</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="B16" s="3" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="22.8">
-      <c r="A18" s="20" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="B19" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="B20" s="9" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="B21" s="9" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="B22" s="9" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="B23" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" s="25" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" s="25" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="B27" s="25" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="23.25">
+      <c r="A29" s="18" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15">
+      <c r="A30" s="7" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="B24" s="28" t="s">
+    <row r="31" spans="1:2" ht="15">
+      <c r="A31" s="7" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="B25" s="28" t="s">
+    <row r="32" spans="1:2" ht="15">
+      <c r="A32" s="7" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="B26" s="28" t="s">
+    <row r="34" spans="1:2" ht="23.25">
+      <c r="A34" s="18" t="s">
         <v>364</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="B27" s="28" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="22.8">
-      <c r="A29" s="20" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="8" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="22.8">
-      <c r="A34" s="20" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="B36" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="B37" s="9" t="s">
-        <v>372</v>
+      <c r="B37" s="8" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="B38" s="9" t="s">
-        <v>373</v>
+      <c r="B38" s="8" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="B39" s="9" t="s">
-        <v>374</v>
+      <c r="B39" s="8" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="B40" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="B41" s="3" t="s">
-        <v>376</v>
+      <c r="B41" s="2" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="B42" s="3" t="s">
-        <v>377</v>
+      <c r="B42" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -10803,304 +12557,304 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H64"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="22.8">
-      <c r="A1" s="31" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="B2" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="B3" s="2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="B4" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="B6" s="2" t="s">
-        <v>408</v>
+    <row r="1" spans="1:3" ht="23.25">
+      <c r="A1" s="28" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15">
+      <c r="B2" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15">
+      <c r="B3" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15">
+      <c r="B4" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15">
+      <c r="B6" s="1" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="C7" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="C8" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="C9" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="C10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="C11" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="C12" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="C13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="23.25">
+      <c r="A16" s="28" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15">
+      <c r="B17" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="15">
+      <c r="B19" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="15">
+      <c r="B21" s="29" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="23.25">
+      <c r="B22" s="30" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="17.25">
+      <c r="B23" s="31" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="22.8">
-      <c r="A16" s="31" t="s">
+    <row r="24" spans="2:8">
+      <c r="C24" s="2" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="2" t="s">
+    <row r="25" spans="2:8" ht="15">
+      <c r="C25" s="12" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="3" t="s">
+    <row r="26" spans="2:8" ht="15">
+      <c r="C26" s="12" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="3" t="s">
+    <row r="27" spans="2:8" ht="15">
+      <c r="B27" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="32" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="22.8">
-      <c r="B22" s="33" t="s">
+    <row r="28" spans="2:8" ht="23.25">
+      <c r="B28" s="18" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" ht="17.399999999999999">
-      <c r="B23" s="34" t="s">
+      <c r="H28" s="32"/>
+    </row>
+    <row r="29" spans="2:8" ht="17.25">
+      <c r="C29" s="6" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="C24" s="3" t="s">
+    <row r="30" spans="2:8">
+      <c r="C30" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="C25" s="14" t="s">
+    <row r="31" spans="2:8">
+      <c r="C31" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="C26" s="14" t="s">
+    <row r="32" spans="2:8">
+      <c r="C32" s="2" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" t="s">
+    <row r="33" spans="1:3" ht="17.25">
+      <c r="C33" s="6" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="22.8">
-      <c r="B28" s="20" t="s">
+    <row r="34" spans="1:3">
+      <c r="C34" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="H28" s="35"/>
-    </row>
-    <row r="29" spans="2:8" ht="17.399999999999999">
-      <c r="C29" s="7" t="s">
+    </row>
+    <row r="35" spans="1:3">
+      <c r="C35" s="8" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="C30" s="3" t="s">
+    <row r="36" spans="1:3">
+      <c r="C36" s="8" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="C31" s="3" t="s">
+    <row r="37" spans="1:3">
+      <c r="C37" s="8" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="32" spans="2:8">
-      <c r="C32" s="3" t="s">
+    <row r="38" spans="1:3">
+      <c r="C38" s="8" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="17.399999999999999">
-      <c r="C33" s="7" t="s">
+    <row r="39" spans="1:3">
+      <c r="C39" s="8" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="C34" s="9" t="s">
+    <row r="40" spans="1:3" ht="17.25">
+      <c r="C40" s="6" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="C35" s="9" t="s">
+    <row r="41" spans="1:3">
+      <c r="C41" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="C36" s="9" t="s">
+    <row r="42" spans="1:3">
+      <c r="C42" s="2" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="C37" s="9" t="s">
+    <row r="43" spans="1:3">
+      <c r="C43" s="9" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="C38" s="9" t="s">
+    <row r="44" spans="1:3">
+      <c r="C44" s="2" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="C39" s="9" t="s">
+    <row r="45" spans="1:3">
+      <c r="C45" s="2" t="s">
         <v>436</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="17.399999999999999">
-      <c r="C40" s="7" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="C41" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="C42" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="C43" s="10" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="C44" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="C45" s="3" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="C46" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="23.25">
+      <c r="A48" s="28" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="17.25">
+      <c r="A49" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15">
+      <c r="A50" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="17.25">
+      <c r="A51" s="6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15">
+      <c r="B52" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15">
+      <c r="B53" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="B54" s="2" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="22.8">
-      <c r="A48" s="31" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="17.399999999999999">
-      <c r="A49" s="7" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="2" t="s">
+    <row r="55" spans="1:2">
+      <c r="B55" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="B56" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="17.399999999999999">
-      <c r="A51" s="7" t="s">
+    <row r="57" spans="1:2">
+      <c r="B57" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="B52" s="3" t="s">
+    <row r="58" spans="1:2" ht="17.25">
+      <c r="A58" s="6" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="B53" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="B54" s="3" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="B55" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="B56" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="B57" s="3" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="17.399999999999999">
-      <c r="A58" s="7" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="B60" s="9" t="s">
-        <v>455</v>
+      <c r="B60" s="8" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="B61" s="9" t="s">
-        <v>456</v>
+      <c r="B61" s="8" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="B62" s="9" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="17.399999999999999">
-      <c r="A63" s="7" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="8" t="s">
-        <v>459</v>
+      <c r="B62" s="8" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="17.25">
+      <c r="A63" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15">
+      <c r="A64" s="7" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
